--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1366,6 +1366,228 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123509809</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>gässjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>577226</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7022347</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123509791</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98376</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>gässjö, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577314</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7022311</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1368,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123509809</v>
+        <v>123509791</v>
       </c>
       <c r="B8" t="n">
         <v>98376</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577226</v>
+        <v>577314</v>
       </c>
       <c r="R8" t="n">
-        <v>7022347</v>
+        <v>7022311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123509791</v>
+        <v>123509809</v>
       </c>
       <c r="B9" t="n">
         <v>98376</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577314</v>
+        <v>577226</v>
       </c>
       <c r="R9" t="n">
-        <v>7022311</v>
+        <v>7022347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,6 +1587,705 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123524649</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97339</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hackspitbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577352</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7022298</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123524567</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97333</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hackspitbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577352</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7022298</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123524715</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>577314</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7022355</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123525121</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97333</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>577308</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7022368</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123525009</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97333</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>577319</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7022353</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123524994</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97333</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>577314</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7022355</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2287,6 +2287,330 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123695969</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hackspittskogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>577279</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7022342</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123695968</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hackspittskogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>577303</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7022340</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123705849</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hackspittskogen, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>577365</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7022295</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123509809</v>
+        <v>123509791</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577226</v>
+        <v>577314</v>
       </c>
       <c r="R8" t="n">
-        <v>7022347</v>
+        <v>7022311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123509791</v>
+        <v>123509809</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577314</v>
+        <v>577226</v>
       </c>
       <c r="R9" t="n">
-        <v>7022311</v>
+        <v>7022347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123524715</v>
+        <v>123525121</v>
       </c>
       <c r="B10" t="n">
-        <v>98379</v>
+        <v>97350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,38 +1602,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577314</v>
+        <v>577308</v>
       </c>
       <c r="R10" t="n">
-        <v>7022355</v>
+        <v>7022368</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123524567</v>
+        <v>123525009</v>
       </c>
       <c r="B11" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,17 +1744,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577352</v>
+        <v>577319</v>
       </c>
       <c r="R11" t="n">
-        <v>7022298</v>
+        <v>7022353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1795,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1805,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123524994</v>
+        <v>123524649</v>
       </c>
       <c r="B12" t="n">
-        <v>97333</v>
+        <v>97356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,16 +1848,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1847,26 +1865,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577314</v>
+        <v>577352</v>
       </c>
       <c r="R12" t="n">
-        <v>7022355</v>
+        <v>7022298</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123525009</v>
+        <v>123524567</v>
       </c>
       <c r="B13" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,26 +1977,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577319</v>
+        <v>577352</v>
       </c>
       <c r="R13" t="n">
-        <v>7022353</v>
+        <v>7022298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524649</v>
+        <v>123524994</v>
       </c>
       <c r="B14" t="n">
-        <v>97339</v>
+        <v>97350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2089,17 +2089,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577352</v>
+        <v>577314</v>
       </c>
       <c r="R14" t="n">
-        <v>7022298</v>
+        <v>7022355</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2150,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123525121</v>
+        <v>123524715</v>
       </c>
       <c r="B15" t="n">
-        <v>97333</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,47 +2189,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577308</v>
+        <v>577314</v>
       </c>
       <c r="R15" t="n">
-        <v>7022368</v>
+        <v>7022355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,7 +2292,7 @@
         <v>123695969</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>123695968</v>
       </c>
       <c r="B17" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>123705849</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -1371,7 +1371,7 @@
         <v>123509791</v>
       </c>
       <c r="B8" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>123509809</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123525121</v>
+        <v>123525009</v>
       </c>
       <c r="B10" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577308</v>
+        <v>577319</v>
       </c>
       <c r="R10" t="n">
-        <v>7022368</v>
+        <v>7022353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123525009</v>
+        <v>123524567</v>
       </c>
       <c r="B11" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,26 +1744,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577319</v>
+        <v>577352</v>
       </c>
       <c r="R11" t="n">
-        <v>7022353</v>
+        <v>7022298</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,7 +1826,7 @@
         <v>123524649</v>
       </c>
       <c r="B12" t="n">
-        <v>97356</v>
+        <v>97373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1944,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524567</v>
+        <v>123524994</v>
       </c>
       <c r="B13" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,17 +1968,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577352</v>
+        <v>577314</v>
       </c>
       <c r="R13" t="n">
-        <v>7022298</v>
+        <v>7022355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524994</v>
+        <v>123524715</v>
       </c>
       <c r="B14" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,37 +2068,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
@@ -2140,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524715</v>
+        <v>123525121</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>97367</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2189,38 +2180,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577314</v>
+        <v>577308</v>
       </c>
       <c r="R15" t="n">
-        <v>7022355</v>
+        <v>7022368</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123695969</v>
+        <v>123705849</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,19 +2324,23 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577279</v>
+        <v>577365</v>
       </c>
       <c r="R16" t="n">
-        <v>7022342</v>
+        <v>7022295</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2377,6 +2381,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2395,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123695968</v>
+        <v>123695969</v>
       </c>
       <c r="B17" t="n">
-        <v>57487</v>
+        <v>98502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,31 +2412,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2440,10 +2444,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577303</v>
+        <v>577279</v>
       </c>
       <c r="R17" t="n">
-        <v>7022340</v>
+        <v>7022342</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2502,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123705849</v>
+        <v>123695968</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>57490</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,46 +2518,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577365</v>
+        <v>577303</v>
       </c>
       <c r="R18" t="n">
-        <v>7022295</v>
+        <v>7022340</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2594,7 +2595,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -1371,7 +1371,7 @@
         <v>123509791</v>
       </c>
       <c r="B8" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>123509809</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>123525009</v>
       </c>
       <c r="B10" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         <v>123524567</v>
       </c>
       <c r="B11" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>123524649</v>
       </c>
       <c r="B12" t="n">
-        <v>97373</v>
+        <v>97375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524994</v>
+        <v>123525121</v>
       </c>
       <c r="B13" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577314</v>
+        <v>577308</v>
       </c>
       <c r="R13" t="n">
-        <v>7022355</v>
+        <v>7022368</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,7 +2059,7 @@
         <v>123524715</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2168,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123525121</v>
+        <v>123524994</v>
       </c>
       <c r="B15" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577308</v>
+        <v>577314</v>
       </c>
       <c r="R15" t="n">
-        <v>7022368</v>
+        <v>7022355</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2292,7 +2292,7 @@
         <v>123705849</v>
       </c>
       <c r="B16" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2400,10 +2400,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123695969</v>
+        <v>123695968</v>
       </c>
       <c r="B17" t="n">
-        <v>98502</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,30 +2412,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2444,10 +2445,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577279</v>
+        <v>577303</v>
       </c>
       <c r="R17" t="n">
-        <v>7022342</v>
+        <v>7022340</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2506,10 +2507,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123695968</v>
+        <v>123695969</v>
       </c>
       <c r="B18" t="n">
-        <v>57490</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2518,31 +2519,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577303</v>
+        <v>577279</v>
       </c>
       <c r="R18" t="n">
-        <v>7022340</v>
+        <v>7022342</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123525121</v>
+        <v>123524715</v>
       </c>
       <c r="B13" t="n">
-        <v>97369</v>
+        <v>98504</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,47 +1947,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577308</v>
+        <v>577314</v>
       </c>
       <c r="R13" t="n">
-        <v>7022368</v>
+        <v>7022355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524715</v>
+        <v>123525121</v>
       </c>
       <c r="B14" t="n">
-        <v>98504</v>
+        <v>97369</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,38 +2059,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577314</v>
+        <v>577308</v>
       </c>
       <c r="R14" t="n">
-        <v>7022355</v>
+        <v>7022368</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -1368,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123509791</v>
+        <v>123509809</v>
       </c>
       <c r="B8" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577314</v>
+        <v>577226</v>
       </c>
       <c r="R8" t="n">
-        <v>7022311</v>
+        <v>7022347</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123509809</v>
+        <v>123509791</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577226</v>
+        <v>577314</v>
       </c>
       <c r="R9" t="n">
-        <v>7022347</v>
+        <v>7022311</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123525009</v>
+        <v>123524567</v>
       </c>
       <c r="B10" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,26 +1623,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577319</v>
+        <v>577352</v>
       </c>
       <c r="R10" t="n">
-        <v>7022353</v>
+        <v>7022298</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123524567</v>
+        <v>123524994</v>
       </c>
       <c r="B11" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,17 +1735,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577352</v>
+        <v>577314</v>
       </c>
       <c r="R11" t="n">
-        <v>7022298</v>
+        <v>7022355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123524649</v>
+        <v>123524715</v>
       </c>
       <c r="B12" t="n">
-        <v>97375</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,38 +1835,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577352</v>
+        <v>577314</v>
       </c>
       <c r="R12" t="n">
-        <v>7022298</v>
+        <v>7022355</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524715</v>
+        <v>123525009</v>
       </c>
       <c r="B13" t="n">
-        <v>98504</v>
+        <v>96957</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,38 +1947,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577314</v>
+        <v>577319</v>
       </c>
       <c r="R13" t="n">
-        <v>7022355</v>
+        <v>7022353</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123525121</v>
+        <v>123524649</v>
       </c>
       <c r="B14" t="n">
-        <v>97369</v>
+        <v>96963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,16 +2072,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2080,26 +2089,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577308</v>
+        <v>577352</v>
       </c>
       <c r="R14" t="n">
-        <v>7022368</v>
+        <v>7022298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524994</v>
+        <v>123525121</v>
       </c>
       <c r="B15" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577314</v>
+        <v>577308</v>
       </c>
       <c r="R15" t="n">
-        <v>7022355</v>
+        <v>7022368</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123705849</v>
+        <v>123695968</v>
       </c>
       <c r="B16" t="n">
-        <v>98504</v>
+        <v>57491</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,46 +2301,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577365</v>
+        <v>577303</v>
       </c>
       <c r="R16" t="n">
-        <v>7022295</v>
+        <v>7022340</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2381,7 +2378,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2400,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123695968</v>
+        <v>123695969</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,31 +2408,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2445,10 +2440,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577303</v>
+        <v>577279</v>
       </c>
       <c r="R17" t="n">
-        <v>7022340</v>
+        <v>7022342</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2507,10 +2502,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123695969</v>
+        <v>123705849</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,19 +2537,23 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577279</v>
+        <v>577365</v>
       </c>
       <c r="R18" t="n">
-        <v>7022342</v>
+        <v>7022295</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2595,6 +2594,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -1368,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123509809</v>
+        <v>123509791</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577226</v>
+        <v>577314</v>
       </c>
       <c r="R8" t="n">
-        <v>7022347</v>
+        <v>7022311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123509791</v>
+        <v>123509809</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577314</v>
+        <v>577226</v>
       </c>
       <c r="R9" t="n">
-        <v>7022311</v>
+        <v>7022347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123524994</v>
+        <v>123525009</v>
       </c>
       <c r="B11" t="n">
         <v>96957</v>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577314</v>
+        <v>577319</v>
       </c>
       <c r="R11" t="n">
-        <v>7022355</v>
+        <v>7022353</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123524715</v>
+        <v>123524994</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,28 +1835,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
@@ -1898,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1908,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,7 +1944,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123525009</v>
+        <v>123525121</v>
       </c>
       <c r="B13" t="n">
         <v>96957</v>
@@ -1970,7 +1979,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1984,10 +1993,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577319</v>
+        <v>577308</v>
       </c>
       <c r="R13" t="n">
-        <v>7022353</v>
+        <v>7022368</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2038,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524649</v>
+        <v>123524715</v>
       </c>
       <c r="B14" t="n">
-        <v>96963</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,38 +2077,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577352</v>
+        <v>577314</v>
       </c>
       <c r="R14" t="n">
-        <v>7022298</v>
+        <v>7022355</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2150,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123525121</v>
+        <v>123524649</v>
       </c>
       <c r="B15" t="n">
-        <v>96957</v>
+        <v>96963</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,16 +2193,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2201,26 +2210,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577308</v>
+        <v>577352</v>
       </c>
       <c r="R15" t="n">
-        <v>7022368</v>
+        <v>7022298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2396,7 +2396,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123695969</v>
+        <v>123705849</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2431,19 +2431,23 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577279</v>
+        <v>577365</v>
       </c>
       <c r="R17" t="n">
-        <v>7022342</v>
+        <v>7022295</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2484,6 +2488,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2502,7 +2507,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123705849</v>
+        <v>123695969</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2537,23 +2542,19 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577365</v>
+        <v>577279</v>
       </c>
       <c r="R18" t="n">
-        <v>7022295</v>
+        <v>7022342</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2594,7 +2595,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -1368,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123509791</v>
+        <v>123509809</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577314</v>
+        <v>577226</v>
       </c>
       <c r="R8" t="n">
-        <v>7022311</v>
+        <v>7022347</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123509809</v>
+        <v>123509791</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577226</v>
+        <v>577314</v>
       </c>
       <c r="R9" t="n">
-        <v>7022347</v>
+        <v>7022311</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123524567</v>
+        <v>123524994</v>
       </c>
       <c r="B10" t="n">
         <v>96957</v>
@@ -1623,17 +1623,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577352</v>
+        <v>577314</v>
       </c>
       <c r="R10" t="n">
-        <v>7022298</v>
+        <v>7022355</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1711,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123525009</v>
+        <v>123524567</v>
       </c>
       <c r="B11" t="n">
         <v>96957</v>
@@ -1735,26 +1744,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577319</v>
+        <v>577352</v>
       </c>
       <c r="R11" t="n">
-        <v>7022353</v>
+        <v>7022298</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,7 +1823,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123524994</v>
+        <v>123525121</v>
       </c>
       <c r="B12" t="n">
         <v>96957</v>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577314</v>
+        <v>577308</v>
       </c>
       <c r="R12" t="n">
-        <v>7022355</v>
+        <v>7022368</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1944,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123525121</v>
+        <v>123524715</v>
       </c>
       <c r="B13" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,47 +1956,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577308</v>
+        <v>577314</v>
       </c>
       <c r="R13" t="n">
-        <v>7022368</v>
+        <v>7022355</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2038,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524715</v>
+        <v>123524649</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,38 +2068,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577314</v>
+        <v>577352</v>
       </c>
       <c r="R14" t="n">
-        <v>7022355</v>
+        <v>7022298</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524649</v>
+        <v>123525009</v>
       </c>
       <c r="B15" t="n">
-        <v>96963</v>
+        <v>96957</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,16 +2184,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2210,17 +2201,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577352</v>
+        <v>577319</v>
       </c>
       <c r="R15" t="n">
-        <v>7022298</v>
+        <v>7022353</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123695968</v>
+        <v>123695969</v>
       </c>
       <c r="B16" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,31 +2301,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2334,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577303</v>
+        <v>577279</v>
       </c>
       <c r="R16" t="n">
-        <v>7022340</v>
+        <v>7022342</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2396,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123705849</v>
+        <v>123695968</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,46 +2407,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577365</v>
+        <v>577303</v>
       </c>
       <c r="R17" t="n">
-        <v>7022295</v>
+        <v>7022340</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2488,7 +2484,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2507,7 +2502,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123695969</v>
+        <v>123705849</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2542,19 +2537,23 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577279</v>
+        <v>577365</v>
       </c>
       <c r="R18" t="n">
-        <v>7022342</v>
+        <v>7022295</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2595,6 +2594,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -1368,7 +1368,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123509809</v>
+        <v>123509791</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577226</v>
+        <v>577314</v>
       </c>
       <c r="R8" t="n">
-        <v>7022347</v>
+        <v>7022311</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123509791</v>
+        <v>123509809</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>350</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577314</v>
+        <v>577226</v>
       </c>
       <c r="R9" t="n">
-        <v>7022311</v>
+        <v>7022347</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123524994</v>
+        <v>123525009</v>
       </c>
       <c r="B10" t="n">
         <v>96957</v>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577314</v>
+        <v>577319</v>
       </c>
       <c r="R10" t="n">
-        <v>7022355</v>
+        <v>7022353</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1823,10 +1823,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123525121</v>
+        <v>123524715</v>
       </c>
       <c r="B12" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,47 +1835,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>577308</v>
+        <v>577314</v>
       </c>
       <c r="R12" t="n">
-        <v>7022368</v>
+        <v>7022355</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1908,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524715</v>
+        <v>123524994</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,28 +1947,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123524649</v>
+        <v>123525121</v>
       </c>
       <c r="B14" t="n">
-        <v>96963</v>
+        <v>96957</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,16 +2072,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2089,17 +2089,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577352</v>
+        <v>577308</v>
       </c>
       <c r="R14" t="n">
-        <v>7022298</v>
+        <v>7022368</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2150,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2177,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123525009</v>
+        <v>123524649</v>
       </c>
       <c r="B15" t="n">
-        <v>96957</v>
+        <v>96963</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,16 +2193,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2201,26 +2210,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577319</v>
+        <v>577352</v>
       </c>
       <c r="R15" t="n">
-        <v>7022353</v>
+        <v>7022298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2395,10 +2395,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123695968</v>
+        <v>123705849</v>
       </c>
       <c r="B17" t="n">
-        <v>57491</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,43 +2407,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577303</v>
+        <v>577365</v>
       </c>
       <c r="R17" t="n">
-        <v>7022340</v>
+        <v>7022295</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2484,6 +2487,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2502,10 +2506,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123705849</v>
+        <v>123695968</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>57491</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2514,46 +2518,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577365</v>
+        <v>577303</v>
       </c>
       <c r="R18" t="n">
-        <v>7022295</v>
+        <v>7022340</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2594,7 +2595,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115334274</v>
+        <v>115334272</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577333</v>
+        <v>577315</v>
       </c>
       <c r="R2" t="n">
-        <v>7022324</v>
+        <v>7022314</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115334272</v>
+        <v>115334281</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,7 +808,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577315</v>
+        <v>577256</v>
       </c>
       <c r="R3" t="n">
-        <v>7022314</v>
+        <v>7022315</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -889,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115334281</v>
+        <v>123695968</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,14 +915,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>gässjö 1, Ång</t>
+          <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577256</v>
+        <v>577303</v>
       </c>
       <c r="R4" t="n">
-        <v>7022315</v>
+        <v>7022340</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -964,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-21</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116900049</v>
+        <v>115334274</v>
       </c>
       <c r="B5" t="n">
-        <v>57929</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,49 +992,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gässjö, Gideåbergsmyrarna, Ång</t>
+          <t>gässjö 1, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577297</v>
+        <v>577333</v>
       </c>
       <c r="R5" t="n">
-        <v>7022346</v>
+        <v>7022324</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1078,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,61 +1071,56 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>André Ahlberg</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>André Ahlberg</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116900041</v>
+        <v>116900122</v>
       </c>
       <c r="B6" t="n">
-        <v>57637</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>102999</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1244,49 +1202,44 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116900122</v>
+        <v>116900041</v>
       </c>
       <c r="B7" t="n">
-        <v>57699</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1368,61 +1321,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123509809</v>
+        <v>116900049</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gässjö, Ång</t>
+          <t>Gässjö, Gideåbergsmyrarna, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577226</v>
+        <v>577297</v>
       </c>
       <c r="R8" t="n">
-        <v>7022347</v>
+        <v>7022346</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1446,12 +1398,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,34 +1422,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>André Ahlberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>André Ahlberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123509791</v>
+        <v>123509714</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1470,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1523,17 +1479,17 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>gässjö, Ång</t>
+          <t>gässjö, Gideåbergsmyrarna, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577314</v>
+        <v>577261</v>
       </c>
       <c r="R9" t="n">
-        <v>7022311</v>
+        <v>7022393</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,59 +1546,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123525121</v>
+        <v>123509791</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>gässjö, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>577308</v>
+        <v>577314</v>
       </c>
       <c r="R10" t="n">
-        <v>7022368</v>
+        <v>7022311</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,22 +1619,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:08</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,68 +1633,72 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123524567</v>
+        <v>123509809</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>gässjö, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>577352</v>
+        <v>577226</v>
       </c>
       <c r="R11" t="n">
-        <v>7022298</v>
+        <v>7022347</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,22 +1725,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:45</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,18 +1739,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1826,12 +1761,7 @@
         <v>123524715</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1935,53 +1865,52 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123524649</v>
+        <v>123695969</v>
       </c>
       <c r="B13" t="n">
-        <v>96985</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Ång</t>
+          <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>577352</v>
+        <v>577279</v>
       </c>
       <c r="R13" t="n">
-        <v>7022298</v>
+        <v>7022342</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2005,22 +1934,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:48</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2035,74 +1954,68 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123525009</v>
+        <v>123705849</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspittskogen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>577319</v>
+        <v>577365</v>
       </c>
       <c r="R14" t="n">
-        <v>7022353</v>
+        <v>7022295</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2126,22 +2039,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:01</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,33 +2053,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123524994</v>
+        <v>123524649</v>
       </c>
       <c r="B15" t="n">
-        <v>96979</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2184,16 +2083,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2201,26 +2100,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>577314</v>
+        <v>577352</v>
       </c>
       <c r="R15" t="n">
-        <v>7022355</v>
+        <v>7022298</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2142,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2152,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,61 +2179,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123705849</v>
+        <v>123524567</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hackspittskogen, Ång</t>
+          <t>Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>577365</v>
+        <v>577352</v>
       </c>
       <c r="R16" t="n">
-        <v>7022295</v>
+        <v>7022298</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2367,12 +2244,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,76 +2268,75 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123695969</v>
+        <v>123524994</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hackspittskogen, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>577279</v>
+        <v>577314</v>
       </c>
       <c r="R17" t="n">
-        <v>7022342</v>
+        <v>7022355</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2474,12 +2360,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,70 +2390,69 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123695968</v>
+        <v>123525009</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hackspittskogen, Ång</t>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>577303</v>
+        <v>577319</v>
       </c>
       <c r="R18" t="n">
-        <v>7022340</v>
+        <v>7022353</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2581,12 +2476,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,15 +2506,131 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123525121</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hackspitbäcken, Hackspitbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>577308</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7022368</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11540-2024 artfynd.xlsx
+++ b/artfynd/A 11540-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115334272</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115334281</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123695968</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115334274</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116900122</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116900041</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116900049</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123509714</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1649,6 +1694,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123509791</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1755,6 +1805,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123509809</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1862,6 +1917,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524715</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1963,6 +2023,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123695969</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2069,6 +2134,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123705849</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2176,6 +2246,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524649</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2283,6 +2358,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524567</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2399,6 +2479,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123524994</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2515,6 +2600,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123525009</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2631,8 +2721,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123525121</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>